--- a/inventario-ti/data/inventario_equipamentos_ti.xlsx
+++ b/inventario-ti/data/inventario_equipamentos_ti.xlsx
@@ -65,7 +65,7 @@
     <t>SN1234523489BR</t>
   </si>
   <si>
-    <t>Emprestado</t>
+    <t>Em manutenção</t>
   </si>
   <si>
     <t>Niteroi II</t>
@@ -956,9 +956,6 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>20</v>
@@ -1146,6 +1143,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/inventario-ti/data/inventario_equipamentos_ti.xlsx
+++ b/inventario-ti/data/inventario_equipamentos_ti.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Inventário" state="visible" r:id="rId4"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="46">
   <si>
     <t>Inventário de Equipamentos de TI</t>
   </si>
@@ -59,13 +59,13 @@
     <t>Acer Aspire 5</t>
   </si>
   <si>
-    <t>BR-LAT005-0002</t>
+    <t>LAPTOP-BAKPUH2T</t>
   </si>
   <si>
     <t>SN1234523489BR</t>
   </si>
   <si>
-    <t>Em manutenção</t>
+    <t>Ativo</t>
   </si>
   <si>
     <t>Niteroi II</t>
@@ -75,6 +75,63 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Celular</t>
+  </si>
+  <si>
+    <t>Poco M5</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Em estoque**</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>GALAXY TAB 8.0</t>
+  </si>
+  <si>
+    <t>SM-T290</t>
+  </si>
+  <si>
+    <t>R9XMC03NKWA</t>
+  </si>
+  <si>
+    <t>Sem user</t>
+  </si>
+  <si>
+    <t>Ipad Apple Mini 1</t>
+  </si>
+  <si>
+    <t>Geração A1432</t>
+  </si>
+  <si>
+    <t>Niterói II</t>
+  </si>
+  <si>
+    <t>Lenovo Tab</t>
+  </si>
+  <si>
+    <t>TB311FU</t>
+  </si>
+  <si>
+    <t>2207121906</t>
+  </si>
+  <si>
+    <t>NIterói II</t>
+  </si>
+  <si>
+    <t>LG K8 Plus</t>
+  </si>
+  <si>
+    <t>X120</t>
+  </si>
+  <si>
+    <t>22071219CG</t>
   </si>
   <si>
     <t>• Preencha uma linha por equipamento. A linha 4 (em itálico) é apenas um exemplo — apague-a ou substitua pelos seus dados.</t>
@@ -105,7 +162,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -115,13 +172,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
@@ -131,7 +188,7 @@
     </font>
     <font>
       <i/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="9"/>
       <name val="Arial"/>
     </font>
@@ -141,14 +198,8 @@
       <sz val="11"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <i/>
-      <color rgb="FF595959"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,41 +208,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-        <bgColor rgb="002E75B6"/>
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill/>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -213,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -221,15 +254,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,9 +564,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
@@ -548,7 +577,7 @@
     <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="27.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,95 +661,235 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46289</v>
+      </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46289</v>
+      </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46289</v>
+      </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46289</v>
+      </c>
       <c r="G8" s="4"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46289</v>
+      </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46289</v>
+      </c>
       <c r="G10" s="4"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46289</v>
+      </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
@@ -958,122 +1127,122 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1101,44 +1270,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>20</v>
+      <c r="A2" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>21</v>
+      <c r="A3" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>22</v>
+      <c r="A4" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>23</v>
+      <c r="A5" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>24</v>
+      <c r="A6" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>25</v>
+      <c r="A7" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
